--- a/outputs/daily/hr_rankings_2026-10-24_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-24_remaining.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>36.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>54.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51</v>
+        <v>53.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>36.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.6</v>
+        <v>50.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>28.5</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1839,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -1864,22 +1880,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.3</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1918,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>54.9</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,131 +1989,139 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>31.84</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2115,12 +2135,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2140,12 +2160,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.9</v>
+        <v>47.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>28.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2253,22 +2269,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2283,67 +2299,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -2376,8 +2392,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2416,12 +2440,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.8</v>
+        <v>47.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2672,7 +2700,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>47</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>36.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2943,24 +2975,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -2968,22 +3000,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.1</v>
+        <v>46.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,62 +3038,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>43.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>54.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3081,12 +3109,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3096,116 +3124,124 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>31.84</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3219,12 +3255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,12 +3280,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>45.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,62 +3318,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3357,7 +3389,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3372,12 +3404,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,67 +3419,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3480,8 +3512,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3495,12 +3535,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3520,12 +3560,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.3</v>
+        <v>38.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,20 +3598,20 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>15.4</v>
       </c>
       <c r="Q12" t="n">
         <v>36.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3581,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3633,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,7 +3684,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -3663,67 +3699,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3756,8 +3792,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3771,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32.9</v>
+        <v>37.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,20 +3878,20 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>36.5</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3909,12 +3949,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3924,7 +3964,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -3939,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4072,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4047,12 +4095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,12 +4120,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
         <v>36.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4185,27 +4229,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,67 +4259,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4308,8 +4352,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4323,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,12 +4400,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.4</v>
+        <v>35.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
         <v>36.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>15.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4632,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4599,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,12 +4680,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>31.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.9</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>23.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4860,8 +4912,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4875,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4900,12 +4960,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.7</v>
+        <v>31.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,65 +4998,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
         <v>28.5</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5013,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5136,8 +5192,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5151,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -5176,22 +5240,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.6</v>
+        <v>30.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,65 +5278,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>27</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5294,7 +5354,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,116 +5364,124 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>31.84</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5427,24 +5495,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -5452,22 +5520,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.2</v>
+        <v>30.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,62 +5558,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>35.4</v>
+        <v>28.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5565,12 +5629,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5580,116 +5644,124 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>31.84</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>36.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6330,12 +6406,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>54.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>28.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51</v>
+        <v>53.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>36.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47.6</v>
+        <v>50.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>28.5</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7133,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -7158,22 +7246,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.3</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,62 +7284,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.6</v>
+        <v>36.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>54.9</v>
+        <v>65.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7271,131 +7355,139 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>31.84</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7409,12 +7501,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7434,12 +7526,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.9</v>
+        <v>47.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>28.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>65.2</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7547,22 +7635,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -7577,67 +7665,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -7670,8 +7758,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7710,12 +7806,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>45.8</v>
+        <v>47.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7966,7 +8066,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>44.4</v>
+        <v>47</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>36.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8237,24 +8341,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -8262,22 +8366,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43.1</v>
+        <v>46.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,62 +8404,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>43.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>54.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8375,12 +8475,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8390,116 +8490,124 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>31.84</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8513,12 +8621,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,12 +8646,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>45.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,62 +8684,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
         <v>28.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8651,7 +8755,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -8666,12 +8770,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,67 +8785,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8774,8 +8878,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8789,12 +8901,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8814,12 +8926,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.3</v>
+        <v>38.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,20 +8964,20 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>15.4</v>
       </c>
       <c r="Q12" t="n">
         <v>36.5</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -8875,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8927,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,7 +9050,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -8957,67 +9065,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9050,8 +9158,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9065,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32.9</v>
+        <v>37.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,20 +9244,20 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>15.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>36.5</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9203,12 +9315,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -9218,7 +9330,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -9233,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9438,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9341,12 +9461,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,12 +9486,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.8</v>
+        <v>36.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
         <v>36.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,27 +9595,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,67 +9625,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9602,8 +9718,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9617,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,12 +9766,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.4</v>
+        <v>35.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
         <v>36.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>15.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +9998,16 @@
           <t>31.84</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9893,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,12 +10046,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>29.8</v>
+        <v>31.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.9</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>23.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10154,8 +10278,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10169,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10194,12 +10326,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.7</v>
+        <v>31.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,65 +10364,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
         <v>28.5</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10307,12 +10435,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10430,8 +10558,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10445,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -10470,22 +10606,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.6</v>
+        <v>30.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,65 +10644,61 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>24.9</v>
+        <v>27</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10588,7 +10720,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,116 +10730,124 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>31.84</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10721,24 +10861,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -10746,22 +10886,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>28.2</v>
+        <v>30.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,62 +10924,58 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>35.4</v>
+        <v>28.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10859,12 +10995,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -10874,116 +11010,124 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>31.84</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>
